--- a/p/ds_25/topic-list_ds.xlsx
+++ b/p/ds_25/topic-list_ds.xlsx
@@ -1,19 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26730" windowHeight="17600" tabRatio="698" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="8960" tabRatio="698" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="core" sheetId="2" r:id="rId1"/>
-    <sheet name="ml" sheetId="17" r:id="rId2"/>
-    <sheet name="deep-learn" sheetId="3" r:id="rId3"/>
-    <sheet name="algorithms" sheetId="5" r:id="rId4"/>
-    <sheet name="ques" sheetId="6" r:id="rId5"/>
-    <sheet name="-" sheetId="8" r:id="rId6"/>
-    <sheet name="learnin-sources" sheetId="20" r:id="rId7"/>
+    <sheet name="deep-learn" sheetId="3" r:id="rId2"/>
+    <sheet name="algorithms" sheetId="5" r:id="rId3"/>
+    <sheet name="ques" sheetId="6" r:id="rId4"/>
+    <sheet name="-" sheetId="8" r:id="rId5"/>
+    <sheet name="learnin-sources" sheetId="20" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="152">
   <si>
     <t>Most basic things</t>
   </si>
@@ -338,13 +337,10 @@
     <t>K-tree</t>
   </si>
   <si>
-    <t>Basic and few extra things</t>
+    <t>Working with data types built-in functions</t>
   </si>
   <si>
     <t>flag</t>
-  </si>
-  <si>
-    <t>Working with data types built-in functions</t>
   </si>
   <si>
     <t>Statistics - A Full University Course on Data Science Basics</t>
@@ -499,12 +495,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -563,30 +559,6 @@
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Bahnschrift"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0C0D0E"/>
-      <name val="Bahnschrift"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Bahnschrift"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Bahnschrift"/>
-      <charset val="0"/>
     </font>
     <font>
       <u/>
@@ -1046,179 +1018,166 @@
     <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1610,79 +1569,79 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" s="22" customFormat="1" ht="28" customHeight="1" spans="1:17">
-      <c r="A2" s="23" t="s">
+    <row r="2" s="13" customFormat="1" ht="28" customHeight="1" spans="1:17">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23" t="s">
+      <c r="D2" s="14"/>
+      <c r="E2" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24" t="s">
+      <c r="F2" s="14"/>
+      <c r="G2" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="25"/>
-      <c r="J2" s="28" t="s">
+      <c r="I2" s="16"/>
+      <c r="J2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28" t="s">
+      <c r="K2" s="19"/>
+      <c r="L2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="28"/>
-      <c r="N2" s="25" t="s">
+      <c r="M2" s="19"/>
+      <c r="N2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25" t="s">
+      <c r="O2" s="16"/>
+      <c r="P2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="Q2" s="25"/>
-    </row>
-    <row r="3" s="22" customFormat="1" customHeight="1" spans="7:17">
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-      <c r="L3" s="29"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-    </row>
-    <row r="4" s="22" customFormat="1" ht="13" customHeight="1" spans="3:17">
+      <c r="Q2" s="16"/>
+    </row>
+    <row r="3" s="13" customFormat="1" customHeight="1" spans="7:17">
+      <c r="G3" s="17"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+    </row>
+    <row r="4" s="13" customFormat="1" ht="13" customHeight="1" spans="3:17">
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18"/>
     </row>
     <row r="5" spans="2:7">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" s="2" t="s">
@@ -1691,7 +1650,7 @@
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="2" t="s">
@@ -1700,19 +1659,19 @@
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="4:7">
       <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="7"/>
+      <c r="G8" s="6"/>
     </row>
     <row r="9" spans="5:7">
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="7"/>
+      <c r="G9" s="6"/>
     </row>
     <row r="11" spans="5:5">
       <c r="E11" s="2" t="s">
@@ -1927,7 +1886,7 @@
       </c>
     </row>
     <row r="51" spans="4:4">
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="11" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1935,19 +1894,19 @@
       <c r="B52" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D52" s="12"/>
+      <c r="D52" s="11"/>
       <c r="E52" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="53" spans="4:5">
-      <c r="D53" s="12"/>
+      <c r="D53" s="11"/>
       <c r="E53" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="54" spans="4:5">
-      <c r="D54" s="12"/>
+      <c r="D54" s="11"/>
       <c r="E54" s="2" t="s">
         <v>71</v>
       </c>
@@ -1956,35 +1915,35 @@
       <c r="B55" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="11" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="56" spans="4:4">
-      <c r="D56" s="12"/>
+      <c r="D56" s="11"/>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="12" t="s">
+      <c r="D57" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="58" spans="4:4">
-      <c r="D58" s="12"/>
+      <c r="D58" s="11"/>
     </row>
     <row r="59" spans="4:4">
-      <c r="D59" s="12"/>
+      <c r="D59" s="11"/>
     </row>
     <row r="60" spans="4:4">
-      <c r="D60" s="12"/>
+      <c r="D60" s="11"/>
     </row>
     <row r="61" spans="3:4">
       <c r="C61" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D61" s="12"/>
+      <c r="D61" s="11"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="2" t="s">
@@ -2091,87 +2050,87 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
       <c r="D85" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="11"/>
+      <c r="A86" s="10"/>
       <c r="D86" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="11"/>
+      <c r="A87" s="10"/>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="11"/>
+      <c r="A88" s="10"/>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="11"/>
+      <c r="A90" s="10"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="13"/>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13"/>
+      <c r="A95" s="12"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
     </row>
     <row r="105" spans="3:5">
-      <c r="C105" s="13"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
     </row>
     <row r="106" spans="3:5">
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
     </row>
     <row r="107" spans="3:5">
-      <c r="C107" s="13"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
     </row>
     <row r="108" spans="3:5">
-      <c r="C108" s="13"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
     </row>
     <row r="109" spans="3:5">
-      <c r="C109" s="13"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
     </row>
     <row r="110" spans="3:5">
-      <c r="C110" s="13"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="12"/>
     </row>
     <row r="111" spans="3:5">
-      <c r="C111" s="13"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
     </row>
     <row r="112" spans="3:5">
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="12"/>
     </row>
     <row r="113" spans="3:5">
-      <c r="C113" s="13"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
     </row>
     <row r="114" spans="3:5">
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="12"/>
     </row>
     <row r="115" spans="3:5">
-      <c r="C115" s="13"/>
-      <c r="D115" s="13"/>
-      <c r="E115" s="13"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2190,599 +2149,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H74"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="14" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="1" width="25.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.8307692307692" style="2" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="2" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="2" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="8.66923076923077" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:2">
-      <c r="B1" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="3:3">
-      <c r="C6" s="12"/>
-    </row>
-    <row r="7" spans="3:3">
-      <c r="C7" s="12"/>
-    </row>
-    <row r="9" spans="3:3">
-      <c r="C9" s="14"/>
-    </row>
-    <row r="11" spans="3:5">
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-    </row>
-    <row r="12" spans="3:5">
-      <c r="C12" s="12"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="12"/>
-    </row>
-    <row r="13" spans="3:5">
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-    </row>
-    <row r="14" spans="3:5">
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-    </row>
-    <row r="15" spans="3:5">
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-    </row>
-    <row r="16" spans="3:5">
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="3:5">
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="3:5">
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="3:5">
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-    </row>
-    <row r="20" spans="3:5">
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-    </row>
-    <row r="21" spans="3:5">
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-    </row>
-    <row r="22" spans="3:5">
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-    </row>
-    <row r="23" spans="3:5">
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-    </row>
-    <row r="24" spans="3:5">
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" s="12"/>
-    </row>
-    <row r="26" spans="3:3">
-      <c r="C26" s="12"/>
-    </row>
-    <row r="27" ht="27" customHeight="1" spans="1:8">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-    </row>
-    <row r="28" ht="16" customHeight="1" spans="1:8">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-    </row>
-    <row r="29" ht="16" customHeight="1" spans="1:8">
-      <c r="A29" s="18"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-    </row>
-    <row r="30" ht="16" customHeight="1" spans="1:8">
-      <c r="A30" s="17"/>
-      <c r="B30" s="16"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-    </row>
-    <row r="31" ht="16" customHeight="1" spans="1:8">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-    </row>
-    <row r="32" ht="16" customHeight="1" spans="1:8">
-      <c r="A32" s="17"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-    </row>
-    <row r="33" ht="16" customHeight="1" spans="1:8">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="16"/>
-    </row>
-    <row r="34" ht="16" customHeight="1" spans="1:8">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="16"/>
-    </row>
-    <row r="35" ht="16" customHeight="1" spans="1:8">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="16"/>
-    </row>
-    <row r="36" ht="16" customHeight="1" spans="1:8">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="16"/>
-    </row>
-    <row r="37" ht="16" customHeight="1" spans="1:8">
-      <c r="A37" s="17"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="16"/>
-    </row>
-    <row r="38" ht="16" customHeight="1" spans="1:8">
-      <c r="A38" s="12"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="16"/>
-    </row>
-    <row r="39" ht="16" customHeight="1" spans="1:8">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="16"/>
-    </row>
-    <row r="40" ht="16" customHeight="1" spans="1:8">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="16"/>
-    </row>
-    <row r="41" ht="16" customHeight="1" spans="1:8">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="16"/>
-    </row>
-    <row r="42" ht="16" customHeight="1" spans="1:8">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="16"/>
-    </row>
-    <row r="43" ht="16" customHeight="1" spans="1:8">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="16"/>
-    </row>
-    <row r="44" ht="16" customHeight="1" spans="1:8">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="16"/>
-    </row>
-    <row r="45" ht="16" customHeight="1" spans="1:8">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="16"/>
-    </row>
-    <row r="46" ht="16" customHeight="1" spans="1:8">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="16"/>
-    </row>
-    <row r="47" ht="16" customHeight="1" spans="1:8">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
-      <c r="D47" s="17"/>
-      <c r="E47" s="17"/>
-      <c r="F47" s="17"/>
-      <c r="G47" s="17"/>
-      <c r="H47" s="16"/>
-    </row>
-    <row r="48" ht="16" customHeight="1" spans="1:8">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="16"/>
-    </row>
-    <row r="49" ht="16" customHeight="1" spans="1:8">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="16"/>
-    </row>
-    <row r="50" ht="16" customHeight="1" spans="1:8">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
-      <c r="H50" s="16"/>
-    </row>
-    <row r="51" ht="16" customHeight="1" spans="1:8">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-      <c r="H51" s="16"/>
-    </row>
-    <row r="52" ht="16" customHeight="1" spans="1:8">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="16"/>
-    </row>
-    <row r="53" ht="16" customHeight="1" spans="1:8">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="16"/>
-    </row>
-    <row r="54" ht="16" customHeight="1" spans="1:8">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
-      <c r="H54" s="16"/>
-    </row>
-    <row r="55" ht="16" customHeight="1" spans="1:8">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="16"/>
-    </row>
-    <row r="56" ht="16" customHeight="1" spans="1:8">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
-      <c r="F56" s="17"/>
-      <c r="G56" s="17"/>
-      <c r="H56" s="16"/>
-    </row>
-    <row r="57" ht="16" customHeight="1" spans="1:8">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="17"/>
-      <c r="G57" s="17"/>
-      <c r="H57" s="16"/>
-    </row>
-    <row r="58" ht="16" customHeight="1" spans="1:8">
-      <c r="A58" s="17"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="16"/>
-    </row>
-    <row r="59" ht="16" customHeight="1" spans="1:8">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="16"/>
-    </row>
-    <row r="60" ht="16" customHeight="1" spans="1:8">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="16"/>
-    </row>
-    <row r="61" ht="16" customHeight="1" spans="1:8">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
-      <c r="D61" s="17"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="16"/>
-    </row>
-    <row r="62" ht="16" customHeight="1" spans="1:8">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="16"/>
-    </row>
-    <row r="63" ht="16" customHeight="1" spans="1:8">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="17"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="16"/>
-    </row>
-    <row r="64" ht="16" customHeight="1" spans="1:8">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
-      <c r="D64" s="17"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="17"/>
-      <c r="G64" s="17"/>
-      <c r="H64" s="16"/>
-    </row>
-    <row r="65" ht="16" customHeight="1" spans="1:8">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="16"/>
-    </row>
-    <row r="66" ht="16" customHeight="1" spans="1:8">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="16"/>
-    </row>
-    <row r="67" ht="16" customHeight="1" spans="1:8">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="17"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="17"/>
-      <c r="G67" s="17"/>
-      <c r="H67" s="16"/>
-    </row>
-    <row r="68" ht="16" customHeight="1" spans="1:8">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
-      <c r="D68" s="17"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="17"/>
-      <c r="G68" s="17"/>
-      <c r="H68" s="16"/>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="12"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-    </row>
-    <row r="72" spans="3:4">
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="20"/>
-      <c r="B73" s="12"/>
-      <c r="C73" s="12"/>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" s="21"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A27:H27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:H99"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="13" customHeight="1" outlineLevelCol="7"/>
   <cols>
@@ -2798,7 +2164,7 @@
   <sheetData>
     <row r="1" ht="14" customHeight="1" spans="2:2">
       <c r="B1" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:8">
@@ -2814,7 +2180,7 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -2822,174 +2188,174 @@
       </c>
     </row>
     <row r="3" customHeight="1" spans="7:7">
-      <c r="G3" s="7"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" customHeight="1" spans="7:7">
-      <c r="G4" s="7"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" customHeight="1" spans="7:7">
-      <c r="G5" s="7"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" customHeight="1" spans="7:7">
-      <c r="G6" s="7"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="16" customHeight="1" spans="2:2">
-      <c r="B16" s="10"/>
+      <c r="B16" s="9"/>
     </row>
     <row r="17" customHeight="1" spans="2:5">
-      <c r="B17" s="10"/>
-      <c r="E17" s="7"/>
+      <c r="B17" s="9"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" customHeight="1" spans="2:2">
-      <c r="B18" s="10"/>
+      <c r="B18" s="9"/>
     </row>
     <row r="19" customHeight="1" spans="2:2">
-      <c r="B19" s="10"/>
+      <c r="B19" s="9"/>
     </row>
     <row r="20" customHeight="1" spans="2:2">
-      <c r="B20" s="10"/>
+      <c r="B20" s="9"/>
     </row>
     <row r="21" customHeight="1" spans="2:2">
-      <c r="B21" s="10"/>
+      <c r="B21" s="9"/>
     </row>
     <row r="22" customHeight="1" spans="2:2">
-      <c r="B22" s="10"/>
+      <c r="B22" s="9"/>
     </row>
     <row r="23" customHeight="1" spans="2:2">
-      <c r="B23" s="10"/>
+      <c r="B23" s="9"/>
     </row>
     <row r="24" customHeight="1" spans="2:2">
-      <c r="B24" s="10"/>
+      <c r="B24" s="9"/>
     </row>
     <row r="25" customHeight="1" spans="2:2">
-      <c r="B25" s="10"/>
+      <c r="B25" s="9"/>
     </row>
     <row r="26" customHeight="1" spans="2:2">
-      <c r="B26" s="11"/>
+      <c r="B26" s="10"/>
     </row>
     <row r="47" customHeight="1" spans="4:4">
-      <c r="D47" s="12"/>
+      <c r="D47" s="11"/>
     </row>
     <row r="67" customHeight="1" spans="3:3">
-      <c r="C67" s="12"/>
+      <c r="C67" s="11"/>
     </row>
     <row r="68" customHeight="1" spans="3:4">
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
     </row>
     <row r="69" customHeight="1" spans="3:3">
-      <c r="C69" s="12"/>
+      <c r="C69" s="11"/>
     </row>
     <row r="70" customHeight="1" spans="3:3">
-      <c r="C70" s="12"/>
+      <c r="C70" s="11"/>
     </row>
     <row r="71" customHeight="1" spans="3:3">
-      <c r="C71" s="12"/>
+      <c r="C71" s="11"/>
     </row>
     <row r="72" customHeight="1" spans="3:3">
-      <c r="C72" s="12"/>
+      <c r="C72" s="11"/>
     </row>
     <row r="73" customHeight="1" spans="3:3">
-      <c r="C73" s="12"/>
+      <c r="C73" s="11"/>
     </row>
     <row r="74" customHeight="1" spans="1:6">
-      <c r="A74" s="13"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
     </row>
     <row r="75" customHeight="1" spans="1:6">
-      <c r="A75" s="13"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
     </row>
     <row r="76" customHeight="1" spans="1:6">
-      <c r="A76" s="13"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
     </row>
     <row r="77" customHeight="1" spans="1:6">
-      <c r="A77" s="13"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
+      <c r="A77" s="12"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
     </row>
     <row r="78" customHeight="1" spans="1:6">
-      <c r="A78" s="13"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
     </row>
     <row r="79" customHeight="1" spans="1:6">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
     </row>
     <row r="80" customHeight="1" spans="1:6">
-      <c r="A80" s="13"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
+      <c r="A80" s="12"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
     </row>
     <row r="81" customHeight="1" spans="1:6">
-      <c r="A81" s="13"/>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
+      <c r="A81" s="12"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
     </row>
     <row r="82" customHeight="1" spans="1:6">
-      <c r="A82" s="13"/>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
+      <c r="A82" s="12"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
     </row>
     <row r="93" customHeight="1" spans="3:4">
-      <c r="C93" s="12"/>
-      <c r="D93" s="12"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
     </row>
     <row r="94" customHeight="1" spans="3:4">
-      <c r="C94" s="12"/>
-      <c r="D94" s="12"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
     </row>
     <row r="95" customHeight="1" spans="3:4">
-      <c r="C95" s="12"/>
-      <c r="D95" s="12"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
     </row>
     <row r="96" customHeight="1" spans="3:4">
-      <c r="C96" s="12"/>
-      <c r="D96" s="12"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
     </row>
     <row r="97" customHeight="1" spans="3:4">
-      <c r="C97" s="12"/>
-      <c r="D97" s="12"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
     </row>
     <row r="98" customHeight="1" spans="4:4">
-      <c r="D98" s="12"/>
+      <c r="D98" s="11"/>
     </row>
     <row r="99" customHeight="1" spans="3:4">
-      <c r="C99" s="12"/>
-      <c r="D99" s="12"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2998,7 +2364,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H20"/>
@@ -3015,7 +2381,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="7:7">
-      <c r="G1" s="7"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
@@ -3030,7 +2396,7 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -3038,136 +2404,136 @@
       </c>
     </row>
     <row r="5" ht="15.5" spans="2:6">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" ht="15.5" spans="2:6">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" ht="15.5" spans="2:6">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" ht="15.5" spans="2:6">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" ht="15.5" spans="2:6">
+      <c r="B8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" ht="15.5" spans="2:6">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" ht="15.5" spans="2:6">
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" ht="15.5" spans="2:6">
+      <c r="B9" s="7"/>
+      <c r="C9" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" ht="15.5" spans="2:6">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" ht="15.5" spans="2:6">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" ht="15.5" spans="2:6">
+      <c r="B11" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" ht="15.5" spans="2:6">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" ht="15.5" spans="2:6">
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" ht="15.5" spans="2:6">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" ht="15.5" spans="2:6">
-      <c r="B12" s="8"/>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" ht="15.5" spans="2:6">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" ht="15.5" spans="2:6">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" ht="15.5" spans="2:6">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" ht="15.5" spans="2:6">
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8" t="s">
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" ht="15.5" spans="2:6">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="15.5" spans="2:6">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" ht="15.5" spans="2:6">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" ht="15.5" spans="2:6">
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" ht="15.5" spans="2:6">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" ht="15.5" spans="2:6">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" ht="15.5" spans="2:6">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" ht="15.5" spans="2:6">
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" ht="15.5" spans="2:6">
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" ht="15.5" spans="2:6">
-      <c r="B19" s="8"/>
-      <c r="C19" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" ht="15.5" spans="2:6">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3180,7 +2546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A2:H2"/>
@@ -3209,7 +2575,7 @@
       <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="H2" s="2" t="s">
@@ -3223,13 +2589,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="16384" width="8.66923076923077" style="6"/>
+    <col min="1" max="16384" width="8.66923076923077" style="5"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3237,7 +2603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E100"/>
@@ -3249,139 +2615,126 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3"/>
       <c r="B2" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="4"/>
-      <c r="C3" s="2" t="s">
+    <row r="4" spans="4:4">
+      <c r="D4" s="2" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4"/>
-      <c r="D4" s="2" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3"/>
       <c r="C5" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="3"/>
       <c r="D6" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="3"/>
       <c r="D7" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="4"/>
+    <row r="9" spans="3:3">
       <c r="C9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="4:4">
+      <c r="D10" s="2" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="4"/>
-      <c r="D10" s="2" t="s">
+    <row r="11" spans="4:4">
+      <c r="D11" s="2" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="4"/>
-      <c r="D11" s="2" t="s">
+    <row r="12" spans="4:4">
+      <c r="D12" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="4"/>
-      <c r="D12" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="4"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="3"/>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="3"/>
       <c r="D15" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3"/>
       <c r="D16" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3"/>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="4"/>
+    <row r="20" spans="2:2">
       <c r="B20" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="4"/>
+        <v>134</v>
+      </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="3"/>
       <c r="B23" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -3390,31 +2743,31 @@
     <row r="25" spans="1:2">
       <c r="A25" s="3"/>
       <c r="B25" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3"/>
       <c r="C26" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="3"/>
       <c r="C27" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
       <c r="C28" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3"/>
       <c r="C29" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -3422,40 +2775,40 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3"/>
       <c r="D32" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3"/>
       <c r="E33" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3"/>
       <c r="E34" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="3"/>
       <c r="D35" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3"/>
       <c r="E36" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:1">
@@ -3463,22 +2816,22 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="3"/>
       <c r="D39" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="3"/>
       <c r="D40" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -3502,18 +2855,9 @@
     <row r="47" spans="1:1">
       <c r="A47" s="3"/>
     </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="4"/>
-    </row>
     <row r="49" spans="1:1">
       <c r="A49" s="3"/>
     </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="4"/>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="4"/>
-    </row>
     <row r="52" spans="1:1">
       <c r="A52" s="3"/>
     </row>
@@ -3532,15 +2876,9 @@
     <row r="57" spans="1:1">
       <c r="A57" s="3"/>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="4"/>
-    </row>
     <row r="59" spans="1:1">
       <c r="A59" s="3"/>
     </row>
-    <row r="60" spans="1:1">
-      <c r="A60" s="4"/>
-    </row>
     <row r="61" spans="1:1">
       <c r="A61" s="3"/>
     </row>
@@ -3559,15 +2897,9 @@
     <row r="66" spans="1:1">
       <c r="A66" s="3"/>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" s="4"/>
-    </row>
     <row r="68" spans="1:1">
       <c r="A68" s="3"/>
     </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="4"/>
-    </row>
     <row r="70" spans="1:1">
       <c r="A70" s="3"/>
     </row>
@@ -3586,15 +2918,9 @@
     <row r="75" spans="1:1">
       <c r="A75" s="3"/>
     </row>
-    <row r="76" spans="1:1">
-      <c r="A76" s="4"/>
-    </row>
     <row r="77" spans="1:1">
       <c r="A77" s="3"/>
     </row>
-    <row r="78" spans="1:1">
-      <c r="A78" s="4"/>
-    </row>
     <row r="79" spans="1:1">
       <c r="A79" s="3"/>
     </row>
@@ -3613,15 +2939,9 @@
     <row r="84" spans="1:1">
       <c r="A84" s="3"/>
     </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="4"/>
-    </row>
     <row r="86" spans="1:1">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1">
-      <c r="A87" s="4"/>
-    </row>
     <row r="88" spans="1:1">
       <c r="A88" s="3"/>
     </row>
@@ -3640,9 +2960,6 @@
     <row r="93" spans="1:1">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" s="4"/>
-    </row>
     <row r="95" spans="1:1">
       <c r="A95" s="3"/>
     </row>
@@ -3650,7 +2967,7 @@
       <c r="A96" s="3"/>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="5"/>
+      <c r="A100" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
